--- a/data/trans_dic/P1416-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P1416-Provincia-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>13,57%</t>
+          <t>10,39%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>5,92%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>9,42%</t>
+          <t>8,16%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>3,08; 9,04</t>
+          <t>3,31; 8,76</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>4,45; 10,38</t>
+          <t>4,72; 10,85</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3,73; 9,46</t>
+          <t>3,56; 9,86</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>8,57; 21,41</t>
+          <t>7,08; 15,34</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2,85; 8,47</t>
+          <t>2,84; 8,43</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>7,33; 15,5</t>
+          <t>7,39; 15,56</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>6,51; 13,64</t>
+          <t>6,23; 13,82</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>3,27; 7,31</t>
+          <t>4,06; 9,11</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>3,63; 7,62</t>
+          <t>3,58; 7,56</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>7,01; 11,87</t>
+          <t>7,02; 12,03</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>5,51; 10,55</t>
+          <t>5,82; 10,54</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>6,55; 14,19</t>
+          <t>6,03; 10,72</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>12,47%</t>
+          <t>12,23%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>12,84%</t>
+          <t>12,61%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>12,66%</t>
+          <t>12,42%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>4,45; 9,03</t>
+          <t>4,57; 9,4</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>4,03; 9,0</t>
+          <t>3,71; 8,64</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,2; 5,9</t>
+          <t>2,22; 5,57</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8,9; 17,33</t>
+          <t>9,15; 16,3</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>8,12; 13,49</t>
+          <t>8,01; 13,53</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,07; 10,14</t>
+          <t>5,01; 9,74</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,43; 9,88</t>
+          <t>5,41; 10,18</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>10,39; 15,73</t>
+          <t>10,1; 15,41</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>6,87; 10,54</t>
+          <t>7,08; 10,59</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4,99; 8,42</t>
+          <t>5,25; 8,49</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4,11; 6,97</t>
+          <t>4,28; 7,26</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>10,49; 15,4</t>
+          <t>10,28; 15,11</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>9,04%</t>
+          <t>9,13%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>10,38%</t>
+          <t>10,22%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>9,75%</t>
+          <t>9,71%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,26; 7,04</t>
+          <t>2,35; 7,18</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,15; 6,9</t>
+          <t>2,13; 6,91</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,35; 6,82</t>
+          <t>2,61; 6,85</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>6,41; 12,91</t>
+          <t>6,35; 13,11</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>4,53; 10,24</t>
+          <t>4,81; 10,56</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,27; 11,56</t>
+          <t>5,23; 11,18</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,19; 6,4</t>
+          <t>2,45; 6,52</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>7,88; 13,86</t>
+          <t>7,7; 13,22</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>4,07; 7,94</t>
+          <t>4,22; 7,81</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>4,25; 8,08</t>
+          <t>4,39; 8,18</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2,92; 5,97</t>
+          <t>2,9; 5,9</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>7,82; 11,99</t>
+          <t>7,81; 11,95</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>5,61%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>5,23%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>5,77; 12,16</t>
+          <t>5,84; 11,87</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,72; 7,34</t>
+          <t>2,77; 7,01</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3,26; 8,67</t>
+          <t>3,23; 8,23</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2,62; 10,29</t>
+          <t>2,62; 9,97</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>8,41; 14,74</t>
+          <t>8,43; 15,06</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>5,28; 11,05</t>
+          <t>5,04; 10,41</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>6,45; 12,36</t>
+          <t>6,51; 12,47</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2,47; 6,8</t>
+          <t>3,81; 8,19</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>7,93; 12,51</t>
+          <t>7,88; 12,4</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>4,38; 7,93</t>
+          <t>4,43; 7,89</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>5,46; 9,4</t>
+          <t>5,35; 9,27</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>2,94; 6,77</t>
+          <t>3,72; 7,69</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>10,35%</t>
+          <t>9,62%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>11,95%</t>
+          <t>11,55%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>11,21%</t>
+          <t>10,63%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>5,21; 13,47</t>
+          <t>5,06; 13,28</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>4,36; 11,84</t>
+          <t>4,27; 11,46</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,92; 9,21</t>
+          <t>2,85; 8,91</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6,95; 15,69</t>
+          <t>6,39; 14,38</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>8,84; 17,98</t>
+          <t>8,39; 18,01</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,34; 17,21</t>
+          <t>8,08; 16,93</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,16; 12,46</t>
+          <t>5,41; 13,21</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>8,94; 15,76</t>
+          <t>8,92; 14,9</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>7,72; 14,09</t>
+          <t>7,87; 14,13</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>7,4; 12,96</t>
+          <t>7,3; 12,76</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>4,75; 9,83</t>
+          <t>4,64; 9,84</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>9,02; 14,24</t>
+          <t>8,46; 13,21</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>13,92%</t>
+          <t>13,93%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>17,6%</t>
+          <t>17,91%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>15,72%</t>
+          <t>15,89%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>3,19; 9,4</t>
+          <t>3,15; 8,73</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3,25; 9,25</t>
+          <t>3,38; 9,93</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3,95; 9,87</t>
+          <t>3,89; 9,64</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>10,34; 18,59</t>
+          <t>10,22; 17,99</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>6,08; 12,76</t>
+          <t>6,03; 12,78</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>3,31; 9,06</t>
+          <t>3,15; 8,97</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>4,5; 10,96</t>
+          <t>4,4; 11,34</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>14,01; 21,88</t>
+          <t>14,19; 21,69</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>5,32; 9,97</t>
+          <t>5,37; 9,88</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>3,96; 8,33</t>
+          <t>3,8; 8,23</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>4,82; 9,16</t>
+          <t>4,85; 9,27</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>13,04; 18,73</t>
+          <t>13,16; 18,53</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>11,47%</t>
+          <t>12,22%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>12,79%</t>
+          <t>17,34%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>12,23%</t>
+          <t>14,88%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2,76; 6,11</t>
+          <t>2,86; 6,23</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2,19; 5,11</t>
+          <t>2,1; 5,01</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,67; 4,67</t>
+          <t>1,66; 4,68</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>8,91; 14,67</t>
+          <t>9,94; 15,46</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>4,7; 8,47</t>
+          <t>4,66; 8,71</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>3,89; 7,73</t>
+          <t>4,05; 7,65</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>5,72; 9,86</t>
+          <t>5,79; 9,97</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>5,86; 17,78</t>
+          <t>14,88; 20,06</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>4,21; 6,79</t>
+          <t>4,17; 6,65</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3,54; 5,84</t>
+          <t>3,58; 5,87</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>4,12; 6,74</t>
+          <t>4,25; 6,75</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>8,03; 15,05</t>
+          <t>13,08; 16,83</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>6,69%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>11,02%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>8,93%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>7,39; 11,49</t>
+          <t>7,23; 11,63</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>3,63; 6,87</t>
+          <t>3,64; 6,87</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>4,75; 8,22</t>
+          <t>4,79; 8,4</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>2,11; 7,81</t>
+          <t>4,91; 8,81</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>10,43; 15,11</t>
+          <t>10,46; 15,37</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,8; 8,3</t>
+          <t>4,94; 8,26</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>7,48; 11,75</t>
+          <t>7,24; 11,42</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>9,14; 13,08</t>
+          <t>9,22; 13,02</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>9,35; 12,54</t>
+          <t>9,48; 12,55</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>4,69; 7,07</t>
+          <t>4,71; 7,17</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>6,65; 9,37</t>
+          <t>6,61; 9,29</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>4,32; 9,55</t>
+          <t>7,48; 10,24</t>
         </is>
       </c>
     </row>
@@ -1784,7 +1784,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>9,41%</t>
+          <t>9,72%</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1804,7 +1804,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>10,79%</t>
+          <t>11,98%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>10,12%</t>
+          <t>10,88%</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>5,9; 7,63</t>
+          <t>5,76; 7,65</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>4,4; 5,93</t>
+          <t>4,37; 5,94</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>4,2; 5,78</t>
+          <t>4,24; 5,71</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>7,39; 10,98</t>
+          <t>8,57; 10,95</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>8,59; 10,59</t>
+          <t>8,64; 10,6</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>6,45; 8,26</t>
+          <t>6,47; 8,25</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>6,85; 8,8</t>
+          <t>7,07; 8,91</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>8,79; 12,09</t>
+          <t>11,07; 13,03</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>7,54; 8,88</t>
+          <t>7,51; 8,92</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>5,71; 6,89</t>
+          <t>5,71; 6,9</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>5,9; 7,15</t>
+          <t>5,88; 7,11</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>8,78; 11,14</t>
+          <t>10,11; 11,61</t>
         </is>
       </c>
     </row>
@@ -2156,7 +2156,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>42247</t>
+          <t>33125</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>14394</t>
+          <t>18695</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>56641</t>
+          <t>51820</t>
         </is>
       </c>
     </row>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>8401; 24668</t>
+          <t>9026; 23908</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>13128; 30601</t>
+          <t>13899; 31970</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>10943; 27803</t>
+          <t>10471; 28973</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>26676; 66679</t>
+          <t>22569; 48905</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>7443; 22096</t>
+          <t>7419; 22001</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>21056; 44529</t>
+          <t>21222; 44698</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>18799; 39370</t>
+          <t>17972; 39890</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>9467; 21184</t>
+          <t>12842; 28807</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>19397; 40699</t>
+          <t>19114; 40362</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>40790; 69088</t>
+          <t>40864; 69995</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>32097; 61443</t>
+          <t>33879; 61413</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>39352; 85307</t>
+          <t>38295; 68069</t>
         </is>
       </c>
     </row>
@@ -2364,7 +2364,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>64533</t>
+          <t>64774</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2384,7 +2384,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>65456</t>
+          <t>68251</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>129989</t>
+          <t>133025</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>21966; 44532</t>
+          <t>22523; 46350</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>20351; 45509</t>
+          <t>18759; 43685</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>11057; 29646</t>
+          <t>11176; 27998</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>46057; 89683</t>
+          <t>48481; 86329</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>40933; 67974</t>
+          <t>40378; 68207</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>26565; 53087</t>
+          <t>26224; 50993</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>28383; 51676</t>
+          <t>28316; 53244</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>52942; 80179</t>
+          <t>54677; 83415</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>68472; 105135</t>
+          <t>70636; 105608</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>51396; 86628</t>
+          <t>54007; 87395</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>42127; 71467</t>
+          <t>43909; 74446</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>107772; 158197</t>
+          <t>110076; 161752</t>
         </is>
       </c>
     </row>
@@ -2572,7 +2572,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>28580</t>
+          <t>28856</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2592,7 +2592,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>36254</t>
+          <t>36414</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2612,7 +2612,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>64834</t>
+          <t>65270</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>7207; 22444</t>
+          <t>7507; 22896</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>6960; 22347</t>
+          <t>6914; 22381</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>7471; 21739</t>
+          <t>8307; 21824</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>20271; 40807</t>
+          <t>20062; 41420</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>15181; 34347</t>
+          <t>16122; 35427</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>17961; 39426</t>
+          <t>17833; 38129</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>7380; 21515</t>
+          <t>8239; 21925</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>27502; 48396</t>
+          <t>27428; 47111</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>26640; 51929</t>
+          <t>27603; 51084</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>28270; 53732</t>
+          <t>29193; 54428</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>19111; 39077</t>
+          <t>18966; 38609</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>51992; 79740</t>
+          <t>52540; 80373</t>
         </is>
       </c>
     </row>
@@ -2780,7 +2780,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>16130</t>
+          <t>17897</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2800,7 +2800,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>20538</t>
+          <t>23685</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2820,7 +2820,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>36668</t>
+          <t>41583</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>20684; 43630</t>
+          <t>20945; 42566</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>10185; 27450</t>
+          <t>10343; 26215</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>12048; 32077</t>
+          <t>11959; 30462</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>8192; 32161</t>
+          <t>9758; 37196</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>31221; 54758</t>
+          <t>31305; 55945</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>20544; 42974</t>
+          <t>19601; 40475</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>24989; 47869</t>
+          <t>25203; 48308</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>11753; 32359</t>
+          <t>16072; 34565</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>57887; 91340</t>
+          <t>57528; 90520</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>33389; 60528</t>
+          <t>33767; 60183</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>41336; 71146</t>
+          <t>40547; 70169</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>23159; 53344</t>
+          <t>29587; 61119</t>
         </is>
       </c>
     </row>
@@ -2988,7 +2988,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>18509</t>
+          <t>19777</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>24806</t>
+          <t>26107</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -3028,7 +3028,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>43315</t>
+          <t>45884</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>10584; 27393</t>
+          <t>10284; 26991</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>9273; 25177</t>
+          <t>9086; 24361</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>6178; 19451</t>
+          <t>6014; 18816</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>12426; 28038</t>
+          <t>13145; 29565</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>18361; 37348</t>
+          <t>17419; 37395</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>18324; 37785</t>
+          <t>17739; 37180</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>11269; 27237</t>
+          <t>11819; 28878</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>18553; 32722</t>
+          <t>20177; 33687</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>31733; 57888</t>
+          <t>32328; 58083</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>32003; 56014</t>
+          <t>31567; 55160</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>20396; 42232</t>
+          <t>19953; 42294</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>34829; 54997</t>
+          <t>36517; 57024</t>
         </is>
       </c>
     </row>
@@ -3196,7 +3196,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>37416</t>
+          <t>37589</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>45117</t>
+          <t>47123</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>82534</t>
+          <t>84712</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>8638; 25458</t>
+          <t>8537; 23648</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>8912; 25335</t>
+          <t>9251; 27219</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>10382; 25971</t>
+          <t>10226; 25359</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>27790; 49965</t>
+          <t>27582; 48557</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>16923; 35497</t>
+          <t>16771; 35534</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>9261; 25379</t>
+          <t>8831; 25120</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>12277; 29928</t>
+          <t>12024; 30961</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>35923; 56090</t>
+          <t>37336; 57069</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>29189; 54714</t>
+          <t>29473; 54244</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>21938; 46130</t>
+          <t>21027; 45577</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>25831; 49122</t>
+          <t>25993; 49731</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>68471; 98344</t>
+          <t>70152; 98744</t>
         </is>
       </c>
     </row>
@@ -3404,7 +3404,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>71160</t>
+          <t>87480</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3424,7 +3424,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>108527</t>
+          <t>133747</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>179686</t>
+          <t>221227</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>16955; 37560</t>
+          <t>17596; 38309</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>14482; 33837</t>
+          <t>13907; 33229</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>10938; 30660</t>
+          <t>10888; 30701</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>55264; 91006</t>
+          <t>71109; 110658</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>29992; 54057</t>
+          <t>29767; 55569</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>26994; 53621</t>
+          <t>28128; 53082</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>39510; 68146</t>
+          <t>40022; 68911</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>49726; 150893</t>
+          <t>114760; 154702</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>52733; 85095</t>
+          <t>52306; 83403</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>47995; 79218</t>
+          <t>48608; 79581</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>55551; 90911</t>
+          <t>57251; 90936</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>117935; 221040</t>
+          <t>194495; 250209</t>
         </is>
       </c>
     </row>
@@ -3612,7 +3612,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>46439</t>
+          <t>53430</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3632,7 +3632,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>77900</t>
+          <t>91158</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3652,7 +3652,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>124339</t>
+          <t>144588</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>54965; 85468</t>
+          <t>53740; 86488</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>28236; 53468</t>
+          <t>28339; 53423</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>36973; 64027</t>
+          <t>37267; 65416</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>19553; 72523</t>
+          <t>39189; 70320</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>81687; 118379</t>
+          <t>81935; 120426</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>39494; 68263</t>
+          <t>40610; 67914</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>61761; 97035</t>
+          <t>59775; 94330</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>64649; 92454</t>
+          <t>75764; 106972</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>142859; 191548</t>
+          <t>144810; 191623</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>75088; 113223</t>
+          <t>75427; 114698</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>106724; 150407</t>
+          <t>106097; 149108</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>70609; 156205</t>
+          <t>121145; 165879</t>
         </is>
       </c>
     </row>
@@ -3820,7 +3820,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>325015</t>
+          <t>342929</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3840,7 +3840,7 @@
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>392992</t>
+          <t>445182</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>718007</t>
+          <t>788111</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>193186; 249909</t>
+          <t>188622; 250643</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>150737; 203071</t>
+          <t>149764; 203598</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>142682; 196124</t>
+          <t>143896; 193843</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>255310; 379206</t>
+          <t>302109; 386344</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>290318; 357888</t>
+          <t>291854; 358099</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>229317; 293884</t>
+          <t>230262; 293374</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>242891; 311813</t>
+          <t>250472; 315818</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>320292; 440376</t>
+          <t>411567; 484539</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>501629; 590728</t>
+          <t>499853; 593898</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>398486; 481127</t>
+          <t>398827; 481472</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>409329; 495829</t>
+          <t>408350; 493309</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>623311; 790962</t>
+          <t>732522; 840964</t>
         </is>
       </c>
     </row>
